--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20221.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -71,6 +71,33 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>JOHAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
   </si>
 </sst>
 </file>
@@ -471,19 +498,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -497,10 +524,10 @@
         <v>30</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>3</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>27</v>
@@ -509,7 +536,7 @@
         <v>90</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -523,19 +550,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>69.23</v>
+        <v>92.31</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -588,16 +615,19 @@
         <v>31</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>31</v>
       </c>
-      <c r="E2">
-        <v>29</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -611,16 +641,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H3">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -634,16 +667,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>65.38</v>
+      </c>
+      <c r="H4">
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -696,19 +732,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -722,19 +758,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>90</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -748,19 +784,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>69.23</v>
+        <v>65.38</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -770,7 +806,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -800,6 +836,75 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920093</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920058</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920111</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20221.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20221.xlsx
@@ -879,7 +879,7 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -902,7 +902,7 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20221.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20221.xlsx
@@ -73,31 +73,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
   </si>
   <si>
     <t>ALAMILLO</t>
   </si>
   <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
+    <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
   </si>
   <si>
     <t>JOHAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
   </si>
 </sst>
 </file>
@@ -838,7 +838,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920093</v>
+        <v>20330051920058</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -853,7 +853,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -861,7 +861,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920058</v>
+        <v>20330051920111</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920111</v>
+        <v>20330051920093</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
@@ -899,10 +899,10 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20221.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -79,25 +79,16 @@
     <t>VALENTE</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>BELLO</t>
   </si>
   <si>
     <t>GAMEZ</t>
   </si>
   <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
     <t>ZURIEL ARTURO</t>
   </si>
   <si>
     <t>ABIUD</t>
-  </si>
-  <si>
-    <t>JOHAN ALEJANDRO</t>
   </si>
 </sst>
 </file>
@@ -744,7 +735,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -770,7 +761,7 @@
         <v>83.33</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -787,13 +778,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>65.38</v>
+        <v>80.77</v>
       </c>
       <c r="H4">
         <v>7.2</v>
@@ -806,7 +797,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -844,10 +835,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -867,10 +858,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -880,29 +871,6 @@
       </c>
       <c r="G3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920093</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20221.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
   <si>
     <t>Mat</t>
   </si>
@@ -71,24 +71,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
   </si>
 </sst>
 </file>
@@ -752,16 +734,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>90</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -778,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>80.77</v>
+        <v>76.92</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -797,7 +779,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -827,52 +809,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920058</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920111</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
